--- a/reports/archive/2026-06-04/nasdaq100_qqq_daily_tracker_2026-06-04.xlsx
+++ b/reports/archive/2026-06-04/nasdaq100_qqq_daily_tracker_2026-06-04.xlsx
@@ -16,12 +16,12 @@
     <sheet name="运行日志" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">AI输入层!$A$1:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">AI输入层!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FMP关键指标!$A$1:$AV$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">FMP可用性!$A$1:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">价格摘要!$A$1:$O$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">分析判断层!$A$1:$C$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">宏观摘要!$A$1:$E$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">宏观摘要!$A$1:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">运行日志!$A$1:$E$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="231">
   <si>
     <t>symbol</t>
   </si>
@@ -79,510 +79,591 @@
     <t>QQQ</t>
   </si>
   <si>
+    <t>alpha_vantage</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>绿色</t>
+  </si>
+  <si>
+    <t>series_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>latest_date</t>
+  </si>
+  <si>
+    <t>latest_value</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>direction</t>
+  </si>
+  <si>
+    <t>DGS10</t>
+  </si>
+  <si>
+    <t>DGS2</t>
+  </si>
+  <si>
+    <t>DGS3MO</t>
+  </si>
+  <si>
+    <t>DFF</t>
+  </si>
+  <si>
+    <t>CPIAUCSL</t>
+  </si>
+  <si>
+    <t>PCEPI</t>
+  </si>
+  <si>
+    <t>UNRATE</t>
+  </si>
+  <si>
+    <t>DGS10_LEVEL_SIGNAL</t>
+  </si>
+  <si>
+    <t>DGS10_1M_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>DGS10_DGS2_SPREAD_SIGNAL</t>
+  </si>
+  <si>
+    <t>CPIAUCSL_3_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>PCEPI_3_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>UNRATE_3M_CHANGE_SIGNAL</t>
+  </si>
+  <si>
+    <t>美国10年期国债收益率</t>
+  </si>
+  <si>
+    <t>美国2年期国债收益率</t>
+  </si>
+  <si>
+    <t>美国3个月国债收益率</t>
+  </si>
+  <si>
+    <t>有效联邦基金利率</t>
+  </si>
+  <si>
+    <t>美国消费者价格指数</t>
+  </si>
+  <si>
+    <t>美国个人消费支出价格指数</t>
+  </si>
+  <si>
+    <t>美国失业率</t>
+  </si>
+  <si>
+    <t>美国10年期国债收益率水平</t>
+  </si>
+  <si>
+    <t>美国10年期国债收益率1月变化</t>
+  </si>
+  <si>
+    <t>2年/10年利差</t>
+  </si>
+  <si>
+    <t>CPI近3次变化</t>
+  </si>
+  <si>
+    <t>PCE近3次变化</t>
+  </si>
+  <si>
+    <t>失业率3个月变化</t>
+  </si>
+  <si>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>信息</t>
+  </si>
+  <si>
+    <t>黄色</t>
+  </si>
+  <si>
+    <t>原始FRED观测值，衍生信号见下方</t>
+  </si>
+  <si>
+    <t>&lt;4.25%绿色，4.25%-5%黄色，&gt;=5%红色</t>
+  </si>
+  <si>
+    <t>&lt;0.15个百分点绿色，0.15-0.30黄色，&gt;=0.30红色</t>
+  </si>
+  <si>
+    <t>正利差绿色，倒挂黄色，深度倒挂或倒挂加深红色</t>
+  </si>
+  <si>
+    <t>近3次环比变化连续上行且最新为正红色，最新上行黄色，否则绿色</t>
+  </si>
+  <si>
+    <t>&lt;0.30个百分点绿色，0.30-0.50黄色，&gt;=0.50红色</t>
+  </si>
+  <si>
+    <t>宏观原始数据</t>
+  </si>
+  <si>
+    <t>长期利率压力</t>
+  </si>
+  <si>
+    <t>长期利率上行速度</t>
+  </si>
+  <si>
+    <t>收益率曲线压力</t>
+  </si>
+  <si>
+    <t>通胀压力，最新指数=332.407</t>
+  </si>
+  <si>
+    <t>通胀压力，最新指数=130.902</t>
+  </si>
+  <si>
+    <t>就业降温速度，最新失业率=4.3</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>rows</t>
+  </si>
+  <si>
+    <t>message</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>MSFT</t>
+  </si>
+  <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>META</t>
+  </si>
+  <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>COST</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>AAPL: quote rows=1</t>
+  </si>
+  <si>
+    <t>MSFT: quote rows=1</t>
+  </si>
+  <si>
+    <t>NVDA: quote rows=1</t>
+  </si>
+  <si>
+    <t>AMZN: quote rows=1</t>
+  </si>
+  <si>
+    <t>META: quote rows=1</t>
+  </si>
+  <si>
+    <t>GOOGL: quote rows=1</t>
+  </si>
+  <si>
+    <t>402 Client Error: Payment Required for url: https://financialmodelingprep.com/stable/quote?symbol=AVGO&amp;apikey=%2A%2A%2AREDACTED%2A%2A%2A</t>
+  </si>
+  <si>
+    <t>TSLA: quote rows=1</t>
+  </si>
+  <si>
+    <t>COST: quote rows=1</t>
+  </si>
+  <si>
+    <t>AMD: quote rows=1</t>
+  </si>
+  <si>
+    <t>fiscalYear</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>reportedCurrency</t>
+  </si>
+  <si>
+    <t>marketCap</t>
+  </si>
+  <si>
+    <t>enterpriseValue</t>
+  </si>
+  <si>
+    <t>evToSales</t>
+  </si>
+  <si>
+    <t>evToOperatingCashFlow</t>
+  </si>
+  <si>
+    <t>evToFreeCashFlow</t>
+  </si>
+  <si>
+    <t>evToEBITDA</t>
+  </si>
+  <si>
+    <t>netDebtToEBITDA</t>
+  </si>
+  <si>
+    <t>currentRatio</t>
+  </si>
+  <si>
+    <t>incomeQuality</t>
+  </si>
+  <si>
+    <t>grahamNumber</t>
+  </si>
+  <si>
+    <t>grahamNetNet</t>
+  </si>
+  <si>
+    <t>taxBurden</t>
+  </si>
+  <si>
+    <t>interestBurden</t>
+  </si>
+  <si>
+    <t>workingCapital</t>
+  </si>
+  <si>
+    <t>investedCapital</t>
+  </si>
+  <si>
+    <t>returnOnAssets</t>
+  </si>
+  <si>
+    <t>operatingReturnOnAssets</t>
+  </si>
+  <si>
+    <t>returnOnTangibleAssets</t>
+  </si>
+  <si>
+    <t>returnOnEquity</t>
+  </si>
+  <si>
+    <t>returnOnInvestedCapital</t>
+  </si>
+  <si>
+    <t>returnOnCapitalEmployed</t>
+  </si>
+  <si>
+    <t>earningsYield</t>
+  </si>
+  <si>
+    <t>freeCashFlowYield</t>
+  </si>
+  <si>
+    <t>capexToOperatingCashFlow</t>
+  </si>
+  <si>
+    <t>capexToDepreciation</t>
+  </si>
+  <si>
+    <t>capexToRevenue</t>
+  </si>
+  <si>
+    <t>salesGeneralAndAdministrativeToRevenue</t>
+  </si>
+  <si>
+    <t>researchAndDevelopementToRevenue</t>
+  </si>
+  <si>
+    <t>stockBasedCompensationToRevenue</t>
+  </si>
+  <si>
+    <t>intangiblesToTotalAssets</t>
+  </si>
+  <si>
+    <t>averageReceivables</t>
+  </si>
+  <si>
+    <t>averagePayables</t>
+  </si>
+  <si>
+    <t>averageInventory</t>
+  </si>
+  <si>
+    <t>daysOfSalesOutstanding</t>
+  </si>
+  <si>
+    <t>daysOfPayablesOutstanding</t>
+  </si>
+  <si>
+    <t>daysOfInventoryOutstanding</t>
+  </si>
+  <si>
+    <t>operatingCycle</t>
+  </si>
+  <si>
+    <t>cashConversionCycle</t>
+  </si>
+  <si>
+    <t>freeCashFlowToEquity</t>
+  </si>
+  <si>
+    <t>freeCashFlowToFirm</t>
+  </si>
+  <si>
+    <t>tangibleAssetValue</t>
+  </si>
+  <si>
+    <t>netCurrentAssetValue</t>
+  </si>
+  <si>
+    <t>2025-09-27</t>
+  </si>
+  <si>
+    <t>2024-09-28</t>
+  </si>
+  <si>
+    <t>2023-09-30</t>
+  </si>
+  <si>
+    <t>2022-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-25</t>
+  </si>
+  <si>
+    <t>2025-06-30</t>
+  </si>
+  <si>
+    <t>2024-06-30</t>
+  </si>
+  <si>
+    <t>2023-06-30</t>
+  </si>
+  <si>
+    <t>2022-06-30</t>
+  </si>
+  <si>
+    <t>2021-06-30</t>
+  </si>
+  <si>
+    <t>2026-01-25</t>
+  </si>
+  <si>
+    <t>2025-01-26</t>
+  </si>
+  <si>
+    <t>2024-01-28</t>
+  </si>
+  <si>
+    <t>2023-01-29</t>
+  </si>
+  <si>
+    <t>2022-01-30</t>
+  </si>
+  <si>
+    <t>2025-12-31</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>2022-12-31</t>
+  </si>
+  <si>
+    <t>2021-12-31</t>
+  </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>FY</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>fmp</t>
+  </si>
+  <si>
+    <t>指标类别</t>
+  </si>
+  <si>
+    <t>指标名称</t>
+  </si>
+  <si>
+    <t>当前值</t>
+  </si>
+  <si>
+    <t>阈值/比较基准</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>数据日期</t>
+  </si>
+  <si>
+    <t>方向/解读</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>风险</t>
+  </si>
+  <si>
+    <t>宏观原始</t>
+  </si>
+  <si>
+    <t>宏观</t>
+  </si>
+  <si>
+    <t>基本面</t>
+  </si>
+  <si>
+    <t>QQQ 20日收益率</t>
+  </si>
+  <si>
+    <t>QQQ 60日收益率</t>
+  </si>
+  <si>
+    <t>QQQ 20日年化波动率</t>
+  </si>
+  <si>
+    <t>QQQ 当前回撤</t>
+  </si>
+  <si>
+    <t>FMP报价可用率</t>
+  </si>
+  <si>
+    <t>&gt;=0绿色，-5%到0黄色，&lt;-5%红色</t>
+  </si>
+  <si>
+    <t>&gt;=0绿色，-10%到0黄色，&lt;-10%红色</t>
+  </si>
+  <si>
+    <t>&lt;25%绿色，25%-35%黄色，&gt;35%红色</t>
+  </si>
+  <si>
+    <t>&gt;-10%绿色，-10%到-15%黄色，&lt;-15%红色</t>
+  </si>
+  <si>
+    <t>&gt;=80%绿色，50%-80%黄色，&lt;50%灰色</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>价格趋势</t>
+  </si>
+  <si>
+    <t>中期趋势</t>
+  </si>
+  <si>
+    <t>波动风险</t>
+  </si>
+  <si>
+    <t>回撤风险</t>
+  </si>
+  <si>
+    <t>基本面数据质量</t>
+  </si>
+  <si>
+    <t>FRED</t>
+  </si>
+  <si>
+    <t>FMP</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>结果</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>综合风险状态</t>
+  </si>
+  <si>
+    <t>数据质量</t>
+  </si>
+  <si>
+    <t>是否允许强化买入</t>
+  </si>
+  <si>
+    <t>较完整</t>
+  </si>
+  <si>
+    <t>仍需仓位确认</t>
+  </si>
+  <si>
+    <t>可按计划执行，但仍需遵守仓位上限。</t>
+  </si>
+  <si>
+    <t>绿色10项，黄色1项，红色0项，灰色0项。</t>
+  </si>
+  <si>
+    <t>本项目不输出无条件买入；所有动作受仓位和风险约束。</t>
+  </si>
+  <si>
+    <t>provider</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
     <t>tiingo</t>
   </si>
   <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>绿色</t>
-  </si>
-  <si>
-    <t>series_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>latest_date</t>
-  </si>
-  <si>
-    <t>latest_value</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>DGS10</t>
-  </si>
-  <si>
-    <t>DGS2</t>
-  </si>
-  <si>
-    <t>DGS3MO</t>
-  </si>
-  <si>
-    <t>DFF</t>
-  </si>
-  <si>
-    <t>CPIAUCSL</t>
-  </si>
-  <si>
-    <t>PCEPI</t>
-  </si>
-  <si>
-    <t>UNRATE</t>
-  </si>
-  <si>
-    <t>美国10年期国债收益率</t>
-  </si>
-  <si>
-    <t>美国2年期国债收益率</t>
-  </si>
-  <si>
-    <t>美国3个月国债收益率</t>
-  </si>
-  <si>
-    <t>有效联邦基金利率</t>
-  </si>
-  <si>
-    <t>美国消费者价格指数</t>
-  </si>
-  <si>
-    <t>美国个人消费支出价格指数</t>
-  </si>
-  <si>
-    <t>美国失业率</t>
-  </si>
-  <si>
-    <t>2026-06-02</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>信息</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>rows</t>
-  </si>
-  <si>
-    <t>message</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>META</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>COST</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>AAPL: quote rows=1</t>
-  </si>
-  <si>
-    <t>MSFT: quote rows=1</t>
-  </si>
-  <si>
-    <t>NVDA: quote rows=1</t>
-  </si>
-  <si>
-    <t>AMZN: quote rows=1</t>
-  </si>
-  <si>
-    <t>META: quote rows=1</t>
-  </si>
-  <si>
-    <t>GOOGL: quote rows=1</t>
-  </si>
-  <si>
-    <t>402 Client Error: Payment Required for url: https://financialmodelingprep.com/stable/quote?symbol=AVGO&amp;apikey=%2A%2A%2AREDACTED%2A%2A%2A</t>
-  </si>
-  <si>
-    <t>TSLA: quote rows=1</t>
-  </si>
-  <si>
-    <t>COST: quote rows=1</t>
-  </si>
-  <si>
-    <t>AMD: quote rows=1</t>
-  </si>
-  <si>
-    <t>fiscalYear</t>
-  </si>
-  <si>
-    <t>period</t>
-  </si>
-  <si>
-    <t>reportedCurrency</t>
-  </si>
-  <si>
-    <t>marketCap</t>
-  </si>
-  <si>
-    <t>enterpriseValue</t>
-  </si>
-  <si>
-    <t>evToSales</t>
-  </si>
-  <si>
-    <t>evToOperatingCashFlow</t>
-  </si>
-  <si>
-    <t>evToFreeCashFlow</t>
-  </si>
-  <si>
-    <t>evToEBITDA</t>
-  </si>
-  <si>
-    <t>netDebtToEBITDA</t>
-  </si>
-  <si>
-    <t>currentRatio</t>
-  </si>
-  <si>
-    <t>incomeQuality</t>
-  </si>
-  <si>
-    <t>grahamNumber</t>
-  </si>
-  <si>
-    <t>grahamNetNet</t>
-  </si>
-  <si>
-    <t>taxBurden</t>
-  </si>
-  <si>
-    <t>interestBurden</t>
-  </si>
-  <si>
-    <t>workingCapital</t>
-  </si>
-  <si>
-    <t>investedCapital</t>
-  </si>
-  <si>
-    <t>returnOnAssets</t>
-  </si>
-  <si>
-    <t>operatingReturnOnAssets</t>
-  </si>
-  <si>
-    <t>returnOnTangibleAssets</t>
-  </si>
-  <si>
-    <t>returnOnEquity</t>
-  </si>
-  <si>
-    <t>returnOnInvestedCapital</t>
-  </si>
-  <si>
-    <t>returnOnCapitalEmployed</t>
-  </si>
-  <si>
-    <t>earningsYield</t>
-  </si>
-  <si>
-    <t>freeCashFlowYield</t>
-  </si>
-  <si>
-    <t>capexToOperatingCashFlow</t>
-  </si>
-  <si>
-    <t>capexToDepreciation</t>
-  </si>
-  <si>
-    <t>capexToRevenue</t>
-  </si>
-  <si>
-    <t>salesGeneralAndAdministrativeToRevenue</t>
-  </si>
-  <si>
-    <t>researchAndDevelopementToRevenue</t>
-  </si>
-  <si>
-    <t>stockBasedCompensationToRevenue</t>
-  </si>
-  <si>
-    <t>intangiblesToTotalAssets</t>
-  </si>
-  <si>
-    <t>averageReceivables</t>
-  </si>
-  <si>
-    <t>averagePayables</t>
-  </si>
-  <si>
-    <t>averageInventory</t>
-  </si>
-  <si>
-    <t>daysOfSalesOutstanding</t>
-  </si>
-  <si>
-    <t>daysOfPayablesOutstanding</t>
-  </si>
-  <si>
-    <t>daysOfInventoryOutstanding</t>
-  </si>
-  <si>
-    <t>operatingCycle</t>
-  </si>
-  <si>
-    <t>cashConversionCycle</t>
-  </si>
-  <si>
-    <t>freeCashFlowToEquity</t>
-  </si>
-  <si>
-    <t>freeCashFlowToFirm</t>
-  </si>
-  <si>
-    <t>tangibleAssetValue</t>
-  </si>
-  <si>
-    <t>netCurrentAssetValue</t>
-  </si>
-  <si>
-    <t>2025-09-27</t>
-  </si>
-  <si>
-    <t>2024-09-28</t>
-  </si>
-  <si>
-    <t>2023-09-30</t>
-  </si>
-  <si>
-    <t>2022-09-24</t>
-  </si>
-  <si>
-    <t>2021-09-25</t>
-  </si>
-  <si>
-    <t>2025-06-30</t>
-  </si>
-  <si>
-    <t>2024-06-30</t>
-  </si>
-  <si>
-    <t>2023-06-30</t>
-  </si>
-  <si>
-    <t>2022-06-30</t>
-  </si>
-  <si>
-    <t>2021-06-30</t>
-  </si>
-  <si>
-    <t>2026-01-25</t>
-  </si>
-  <si>
-    <t>2025-01-26</t>
-  </si>
-  <si>
-    <t>2024-01-28</t>
-  </si>
-  <si>
-    <t>2023-01-29</t>
-  </si>
-  <si>
-    <t>2022-01-30</t>
-  </si>
-  <si>
-    <t>2025-12-31</t>
-  </si>
-  <si>
-    <t>2024-12-31</t>
-  </si>
-  <si>
-    <t>2023-12-31</t>
-  </si>
-  <si>
-    <t>2022-12-31</t>
-  </si>
-  <si>
-    <t>2021-12-31</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2026</t>
-  </si>
-  <si>
-    <t>FY</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>fmp</t>
-  </si>
-  <si>
-    <t>指标类别</t>
-  </si>
-  <si>
-    <t>指标名称</t>
-  </si>
-  <si>
-    <t>当前值</t>
-  </si>
-  <si>
-    <t>阈值/比较基准</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>数据日期</t>
-  </si>
-  <si>
-    <t>方向/解读</t>
-  </si>
-  <si>
-    <t>来源</t>
-  </si>
-  <si>
-    <t>价格</t>
-  </si>
-  <si>
-    <t>风险</t>
-  </si>
-  <si>
-    <t>宏观</t>
-  </si>
-  <si>
-    <t>基本面</t>
-  </si>
-  <si>
-    <t>QQQ 20日收益率</t>
-  </si>
-  <si>
-    <t>QQQ 60日收益率</t>
-  </si>
-  <si>
-    <t>QQQ 20日年化波动率</t>
-  </si>
-  <si>
-    <t>QQQ 当前回撤</t>
-  </si>
-  <si>
-    <t>FMP报价可用率</t>
-  </si>
-  <si>
-    <t>&gt;=0绿色，-5%到0黄色，&lt;-5%红色</t>
-  </si>
-  <si>
-    <t>&gt;=0绿色，-10%到0黄色，&lt;-10%红色</t>
-  </si>
-  <si>
-    <t>&lt;25%绿色，25%-35%黄色，&gt;35%红色</t>
-  </si>
-  <si>
-    <t>&gt;-10%绿色，-10%到-15%黄色，&lt;-15%红色</t>
-  </si>
-  <si>
-    <t>用于方向判断</t>
-  </si>
-  <si>
-    <t>&gt;=80%绿色，50%-80%黄色，&lt;50%灰色</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>价格趋势</t>
-  </si>
-  <si>
-    <t>中期趋势</t>
-  </si>
-  <si>
-    <t>波动风险</t>
-  </si>
-  <si>
-    <t>回撤风险</t>
-  </si>
-  <si>
-    <t>宏观环境</t>
-  </si>
-  <si>
-    <t>基本面数据质量</t>
-  </si>
-  <si>
-    <t>FRED</t>
-  </si>
-  <si>
-    <t>FMP</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>结果</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>综合风险状态</t>
-  </si>
-  <si>
-    <t>数据质量</t>
-  </si>
-  <si>
-    <t>是否允许强化买入</t>
-  </si>
-  <si>
-    <t>较完整</t>
-  </si>
-  <si>
-    <t>仍需仓位确认</t>
-  </si>
-  <si>
-    <t>可按计划执行，但仍需遵守仓位上限。</t>
-  </si>
-  <si>
-    <t>绿色5项，黄色0项，红色0项，灰色0项。</t>
-  </si>
-  <si>
-    <t>本项目不输出无条件买入；所有动作受仓位和风险约束。</t>
-  </si>
-  <si>
-    <t>provider</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>alpha_vantage</t>
-  </si>
-  <si>
     <t>fred</t>
   </si>
   <si>
@@ -601,7 +682,7 @@
     <t>key_metrics</t>
   </si>
   <si>
-    <t>Thank you for using Alpha Vantage! This is a premium endpoint. You may subscribe to any of the premium plans at https://www.alphavantage.co/premium/ to instantly unlock all premium endpoints</t>
+    <t>QQQ: 100 rows</t>
   </si>
   <si>
     <t>QQQ: 288 rows</t>
@@ -1087,7 +1168,7 @@
         <v>0.09184137556667316</v>
       </c>
       <c r="F2" s="1">
-        <v>0.2260390669904588</v>
+        <v>0.2245129656443334</v>
       </c>
       <c r="G2" s="1">
         <v>0.1576653841519145</v>
@@ -1096,13 +1177,10 @@
         <v>-0.002613380508201923</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.1196618032822726</v>
+        <v>-0.1183474937620417</v>
       </c>
       <c r="J2">
         <v>662.3317999999999</v>
-      </c>
-      <c r="K2">
-        <v>619.3427941110641</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>18</v>
@@ -1125,7 +1203,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1133,9 +1211,10 @@
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>19</v>
       </c>
@@ -1151,128 +1230,314 @@
       <c r="E1" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D2">
         <v>4.46</v>
       </c>
       <c r="E2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D3">
         <v>4.05</v>
       </c>
       <c r="E3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>3.77</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>3.62</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>56</v>
+      </c>
+      <c r="G5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D6">
         <v>332.407</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D7">
         <v>130.902</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>56</v>
+      </c>
+      <c r="G7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D8">
         <v>4.3</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9">
+        <v>4.46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12">
+        <v>0.006400377846336402</v>
+      </c>
+      <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13">
+        <v>0.003995981009502714</v>
+      </c>
+      <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>61</v>
+      </c>
+      <c r="G14" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E8"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1290,18 +1555,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B2" t="b">
         <v>1</v>
@@ -1310,12 +1575,12 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B3" t="b">
         <v>1</v>
@@ -1324,12 +1589,12 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -1338,12 +1603,12 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B5" t="b">
         <v>1</v>
@@ -1352,12 +1617,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B6" t="b">
         <v>1</v>
@@ -1366,12 +1631,12 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B7" t="b">
         <v>1</v>
@@ -1380,12 +1645,12 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B8" t="b">
         <v>0</v>
@@ -1394,12 +1659,12 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -1408,12 +1673,12 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="B10" t="b">
         <v>1</v>
@@ -1422,12 +1687,12 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B11" t="b">
         <v>1</v>
@@ -1436,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1503,139 +1768,139 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="Y1" s="2" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="AA1" s="2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="AB1" s="2" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="AC1" s="2" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="AF1" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="AG1" s="2" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="AJ1" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="AK1" s="2" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="AL1" s="2" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="AM1" s="2" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="AO1" s="2" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="AP1" s="2" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="AQ1" s="2" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="AR1" s="2" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="AS1" s="2" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="AU1" s="2" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="AV1" s="2" t="s">
         <v>1</v>
@@ -1643,19 +1908,19 @@
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C2" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E2" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F2">
         <v>3818743810000</v>
@@ -1784,24 +2049,24 @@
         <v>-137551000000</v>
       </c>
       <c r="AV2" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E3" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F3">
         <v>3495160329570</v>
@@ -1930,24 +2195,24 @@
         <v>-155043000000</v>
       </c>
       <c r="AV3" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="C4" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F4">
         <v>2695569789510</v>
@@ -2076,24 +2341,24 @@
         <v>-146871000000</v>
       </c>
       <c r="AV4" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E5" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F5">
         <v>2439367314090</v>
@@ -2222,24 +2487,24 @@
         <v>-166678000000</v>
       </c>
       <c r="AV5" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="C6" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F6">
         <v>2453750882240</v>
@@ -2368,24 +2633,24 @@
         <v>-153076000000</v>
       </c>
       <c r="AV6" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E7" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F7">
         <v>3697248530000</v>
@@ -2514,24 +2779,24 @@
         <v>-84393000000</v>
       </c>
       <c r="AV7" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>115</v>
+        <v>143</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F8">
         <v>3393960630000</v>
@@ -2660,24 +2925,24 @@
         <v>-83952000000</v>
       </c>
       <c r="AV8" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="C9" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F9">
         <v>2535660840000</v>
@@ -2806,24 +3071,24 @@
         <v>-21496000000</v>
       </c>
       <c r="AV9" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F10">
         <v>1925197680000</v>
@@ -2952,24 +3217,24 @@
         <v>-28614000000</v>
       </c>
       <c r="AV10" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F11">
         <v>2044482300000</v>
@@ -3098,24 +3363,24 @@
         <v>-7385000000</v>
       </c>
       <c r="AV11" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="D12" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E12" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F12">
         <v>4542222730000</v>
@@ -3244,24 +3509,24 @@
         <v>76095000000</v>
       </c>
       <c r="AV12" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C13" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E13" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F13">
         <v>2907803100000</v>
@@ -3390,24 +3655,24 @@
         <v>47852000000</v>
       </c>
       <c r="AV13" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C14" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F14">
         <v>1542384300000</v>
@@ -3536,24 +3801,24 @@
         <v>21595000000</v>
       </c>
       <c r="AV14" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F15">
         <v>476509200000</v>
@@ -3682,24 +3947,24 @@
         <v>3992000000</v>
       </c>
       <c r="AV15" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C16" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D16" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E16" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F16">
         <v>611270400000</v>
@@ -3828,24 +4093,24 @@
         <v>11254000000</v>
       </c>
       <c r="AV16" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:48">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F17">
         <v>2459617920000</v>
@@ -3974,24 +4239,24 @@
         <v>-177894000000</v>
       </c>
       <c r="AV17" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:48">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B18" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F18">
         <v>2297671470000</v>
@@ -4120,24 +4385,24 @@
         <v>-148057000000</v>
       </c>
       <c r="AV18" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:48">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C19" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E19" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F19">
         <v>1565589760000</v>
@@ -4266,24 +4531,24 @@
         <v>-153628000000</v>
       </c>
       <c r="AV19" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:48">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C20" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D20" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E20" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F20">
         <v>855876000000</v>
@@ -4409,24 +4674,24 @@
         <v>-169841000000</v>
       </c>
       <c r="AV20" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:48">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E21" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F21">
         <v>1687206400000</v>
@@ -4555,24 +4820,24 @@
         <v>-120724000000</v>
       </c>
       <c r="AV21" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:48">
       <c r="A22" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E22" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F22">
         <v>1664086890000</v>
@@ -4701,24 +4966,24 @@
         <v>-40056000000</v>
       </c>
       <c r="AV22" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:48">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F23">
         <v>1483682340000</v>
@@ -4847,24 +5112,24 @@
         <v>6628000000</v>
       </c>
       <c r="AV23" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:48">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F24">
         <v>911093040000</v>
@@ -4993,24 +5258,24 @@
         <v>8910000000</v>
       </c>
       <c r="AV24" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:48">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>155</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>160</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F25">
         <v>323353580000</v>
@@ -5139,24 +5404,24 @@
         <v>-465000000</v>
       </c>
       <c r="AV25" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:48">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B26" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
+        <v>163</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="F26">
         <v>946825250000.0001</v>
@@ -5285,7 +5550,7 @@
         <v>25558000000</v>
       </c>
       <c r="AV26" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5296,7 +5561,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="12.7109375" customWidth="1"/>
@@ -5304,42 +5569,42 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="C2">
         <v>0.09184137556667316</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -5348,7 +5613,7 @@
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -5356,16 +5621,16 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="C3">
-        <v>0.2260390669904588</v>
+        <v>0.2245129656443334</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -5374,7 +5639,7 @@
         <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -5382,16 +5647,16 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>181</v>
       </c>
       <c r="C4">
         <v>0.1576653841519145</v>
       </c>
       <c r="D4" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -5400,7 +5665,7 @@
         <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -5408,16 +5673,16 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="C5">
         <v>-0.002613380508201923</v>
       </c>
       <c r="D5" t="s">
-        <v>158</v>
+        <v>187</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -5426,7 +5691,7 @@
         <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -5434,214 +5699,370 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>4.46</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C7">
         <v>4.05</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H7" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>3.77</v>
       </c>
       <c r="D8" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C9">
         <v>3.62</v>
       </c>
       <c r="D9" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H9" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C10">
         <v>332.407</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>130.902</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G11" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C12">
         <v>4.3</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F12" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G12" t="s">
-        <v>166</v>
+        <v>62</v>
       </c>
       <c r="H12" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
-        <v>154</v>
+        <v>46</v>
       </c>
       <c r="C13">
+        <v>4.46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>177</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14">
+        <v>0.07000000000000028</v>
+      </c>
+      <c r="D14" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H14" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>177</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H15" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16">
+        <v>0.006400377846336402</v>
+      </c>
+      <c r="D16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>0.003995981009502714</v>
+      </c>
+      <c r="D17" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" t="s">
+        <v>67</v>
+      </c>
+      <c r="H17" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" t="s">
+        <v>68</v>
+      </c>
+      <c r="H18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19">
         <v>0.9</v>
       </c>
-      <c r="D13" t="s">
-        <v>160</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D19" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="F13" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" t="s">
-        <v>167</v>
-      </c>
-      <c r="H13" t="s">
-        <v>169</v>
+      <c r="F19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G19" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H13"/>
+  <autoFilter ref="A1:H19"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5656,46 +6077,46 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="C3" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -5714,44 +6135,44 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>190</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="B3" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -5760,381 +6181,381 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B6" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>194</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B9" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>184</v>
+        <v>211</v>
       </c>
       <c r="B10" t="s">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B11" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B16" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B17" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B18" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B19" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B22" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>201</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B24" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="D24" t="b">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="B25" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D25" t="b">
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>203</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
